--- a/Homework_creater/config.xlsx
+++ b/Homework_creater/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>sheet名称</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>homework/ttk</t>
+  </si>
+  <si>
+    <t>enemy</t>
+  </si>
+  <si>
+    <t>templates/template_enemy.txt</t>
+  </si>
+  <si>
+    <t>homework/enemy</t>
   </si>
 </sst>
 </file>
@@ -995,8 +1004,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11.9557522123894" customWidth="1"/>
     <col min="2" max="2" width="28.8761061946903" customWidth="1"/>
@@ -1045,6 +1054,17 @@
       </c>
       <c r="C4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
